--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,6 +1294,2651 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126531500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105381</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>758915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7202118</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126531508</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>758774</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7202026</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126531544</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>758912</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7202106</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126531505</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>758910</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7202078</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126531548</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>758798</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7201814</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126531608</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>758776</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7201970</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126531503</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>758834</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7201929</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126531509</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>758758</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7201973</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126531552</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>758900</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7202051</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126531502</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91603</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>758757</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7201974</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126531534</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>758902</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7202060</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tupp</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126531566</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>758822</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7202153</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126531536</v>
+      </c>
+      <c r="B19" t="n">
+        <v>103803</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>758765</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7201809</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126531529</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>758759</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7201850</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126531575</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>758883</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7202117</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126531510</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>758881</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7201998</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126531580</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>758845</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7201911</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126531546</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>758837</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7201925</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126531618</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>758798</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7201791</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126531532</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57479</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>758836</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7201985</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126531610</v>
+      </c>
+      <c r="B27" t="n">
+        <v>105396</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>758880</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7201997</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126531595</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>758795</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7201807</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126531551</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>758870</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7201971</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126531569</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98395</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>758904</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7202090</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126531600</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>758907</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7202075</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126531577</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>758824</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7202146</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126531579</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>758737</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7201862</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,32 +1490,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126531548</v>
+        <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>98382</v>
+        <v>91319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758798</v>
+        <v>758910</v>
       </c>
       <c r="R9" t="n">
-        <v>7201814</v>
+        <v>7202078</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,32 +1684,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126531505</v>
+        <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>98457</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758910</v>
+        <v>758798</v>
       </c>
       <c r="R11" t="n">
-        <v>7202078</v>
+        <v>7201814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,32 +1878,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126531502</v>
+        <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91603</v>
+        <v>91319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758757</v>
+        <v>758834</v>
       </c>
       <c r="R13" t="n">
-        <v>7201974</v>
+        <v>7201929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1978,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,32 +2072,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126531552</v>
+        <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>98382</v>
+        <v>91677</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758900</v>
+        <v>758757</v>
       </c>
       <c r="R15" t="n">
-        <v>7202051</v>
+        <v>7201974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,32 +2169,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126531503</v>
+        <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>91245</v>
+        <v>98457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758834</v>
+        <v>758900</v>
       </c>
       <c r="R16" t="n">
-        <v>7201929</v>
+        <v>7202051</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126531566</v>
+        <v>126531534</v>
       </c>
       <c r="B17" t="n">
-        <v>80111</v>
+        <v>56849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,21 +2277,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2301,10 +2301,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758822</v>
+        <v>758902</v>
       </c>
       <c r="R17" t="n">
-        <v>7202153</v>
+        <v>7202060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,6 +2337,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2368,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126531534</v>
+        <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>56849</v>
+        <v>80142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,21 +2379,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2403,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758902</v>
+        <v>758822</v>
       </c>
       <c r="R18" t="n">
-        <v>7202060</v>
+        <v>7202153</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,11 +2439,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,7 +2468,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>103803</v>
+        <v>103878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2866,32 +2866,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126531546</v>
+        <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>98382</v>
+        <v>80114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2901,10 +2901,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>758837</v>
+        <v>758845</v>
       </c>
       <c r="R23" t="n">
-        <v>7201925</v>
+        <v>7201911</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,32 +2963,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126531580</v>
+        <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>98457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>758845</v>
+        <v>758837</v>
       </c>
       <c r="R24" t="n">
-        <v>7201911</v>
+        <v>7201925</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126531569</v>
+        <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98395</v>
+        <v>98457</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758904</v>
+        <v>758870</v>
       </c>
       <c r="R29" t="n">
-        <v>7202090</v>
+        <v>7201971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126531551</v>
+        <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98382</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,16 +3564,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758870</v>
+        <v>758904</v>
       </c>
       <c r="R30" t="n">
-        <v>7201971</v>
+        <v>7202090</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126531579</v>
+        <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>758737</v>
+        <v>758824</v>
       </c>
       <c r="R32" t="n">
-        <v>7201862</v>
+        <v>7202146</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126531577</v>
+        <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>758824</v>
+        <v>758737</v>
       </c>
       <c r="R33" t="n">
-        <v>7202146</v>
+        <v>7201862</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3939,6 +3939,1300 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128504673</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>758853</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7202114</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128504665</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>758866</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7202091</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128505054</v>
+      </c>
+      <c r="B36" t="n">
+        <v>104016</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>758796</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7201797</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128504656</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>758756</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7201855</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128505057</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>758900</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7202049</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128505058</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>758801</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7201796</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128505052</v>
+      </c>
+      <c r="B40" t="n">
+        <v>104016</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>758800</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7201804</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128504674</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>758861</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7202117</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128504681</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>758862</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7202121</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128504683</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>758882</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7202131</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Bild 6</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128504658</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97454</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>758903</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7202078</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128504664</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>758894</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7202071</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128505060</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>758897</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7202042</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bild 4</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4643,7 +4643,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128504674</v>
+        <v>128504681</v>
       </c>
       <c r="B41" t="n">
         <v>98571</v>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758861</v>
+        <v>758862</v>
       </c>
       <c r="R41" t="n">
-        <v>7202117</v>
+        <v>7202121</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128504681</v>
+        <v>128504674</v>
       </c>
       <c r="B42" t="n">
         <v>98571</v>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>758862</v>
+        <v>758861</v>
       </c>
       <c r="R42" t="n">
-        <v>7202121</v>
+        <v>7202117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4237,53 +4237,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128504656</v>
+        <v>128505052</v>
       </c>
       <c r="B37" t="n">
-        <v>57685</v>
+        <v>104016</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758756</v>
+        <v>758800</v>
       </c>
       <c r="R37" t="n">
-        <v>7201855</v>
+        <v>7201804</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4316,11 +4308,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4347,45 +4334,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505057</v>
+        <v>128504656</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758900</v>
+        <v>758756</v>
       </c>
       <c r="R38" t="n">
-        <v>7202049</v>
+        <v>7201855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4417,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4449,7 +4444,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505058</v>
+        <v>128505057</v>
       </c>
       <c r="B39" t="n">
         <v>98571</v>
@@ -4484,10 +4479,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758801</v>
+        <v>758900</v>
       </c>
       <c r="R39" t="n">
-        <v>7201796</v>
+        <v>7202049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4520,6 +4515,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505052</v>
+        <v>128505058</v>
       </c>
       <c r="B40" t="n">
-        <v>104016</v>
+        <v>98571</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758800</v>
+        <v>758801</v>
       </c>
       <c r="R40" t="n">
-        <v>7201804</v>
+        <v>7201796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>104016</v>
+        <v>104028</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4237,45 +4237,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128505052</v>
+        <v>128504656</v>
       </c>
       <c r="B37" t="n">
-        <v>104016</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758800</v>
+        <v>758756</v>
       </c>
       <c r="R37" t="n">
-        <v>7201804</v>
+        <v>7201855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4308,6 +4316,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4334,53 +4347,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>57685</v>
+        <v>98579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R38" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4417,7 +4422,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4444,10 +4449,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505057</v>
+        <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4479,10 +4484,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758900</v>
+        <v>758801</v>
       </c>
       <c r="R39" t="n">
-        <v>7202049</v>
+        <v>7201796</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,11 +4520,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505058</v>
+        <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>104028</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758801</v>
+        <v>758800</v>
       </c>
       <c r="R40" t="n">
-        <v>7201796</v>
+        <v>7201804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B35" t="n">
-        <v>80192</v>
+        <v>104036</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R35" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,11 +4109,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,32 +4135,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B36" t="n">
-        <v>104028</v>
+        <v>80192</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4175,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R36" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,6 +4206,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,7 +4350,7 @@
         <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>104036</v>
+        <v>80192</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R35" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,6 +4109,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4135,32 +4140,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>80192</v>
+        <v>104036</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4175,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R36" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,11 +4211,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4347,32 +4347,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505057</v>
+        <v>128505052</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>104036</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758900</v>
+        <v>758800</v>
       </c>
       <c r="R38" t="n">
-        <v>7202049</v>
+        <v>7201804</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4418,11 +4418,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4449,7 +4444,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505058</v>
+        <v>128505057</v>
       </c>
       <c r="B39" t="n">
         <v>98585</v>
@@ -4484,10 +4479,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758801</v>
+        <v>758900</v>
       </c>
       <c r="R39" t="n">
-        <v>7201796</v>
+        <v>7202049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4520,6 +4515,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505052</v>
+        <v>128505058</v>
       </c>
       <c r="B40" t="n">
-        <v>104036</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758800</v>
+        <v>758801</v>
       </c>
       <c r="R40" t="n">
-        <v>7201804</v>
+        <v>7201796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B35" t="n">
-        <v>80192</v>
+        <v>104048</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R35" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,11 +4109,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,32 +4135,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B36" t="n">
-        <v>104036</v>
+        <v>80194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4175,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R36" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,6 +4206,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4237,53 +4237,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R37" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4312,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4347,32 +4339,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505052</v>
+        <v>128505058</v>
       </c>
       <c r="B38" t="n">
-        <v>104036</v>
+        <v>98588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4382,10 +4374,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758800</v>
+        <v>758801</v>
       </c>
       <c r="R38" t="n">
-        <v>7201804</v>
+        <v>7201796</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4444,45 +4436,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505057</v>
+        <v>128504656</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758900</v>
+        <v>758756</v>
       </c>
       <c r="R39" t="n">
-        <v>7202049</v>
+        <v>7201855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Bild 3</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505058</v>
+        <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>104048</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758801</v>
+        <v>758800</v>
       </c>
       <c r="R40" t="n">
-        <v>7201796</v>
+        <v>7201804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>104048</v>
+        <v>80194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R35" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,6 +4109,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4135,32 +4140,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>80194</v>
+        <v>104057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4175,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R36" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,11 +4211,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4237,45 +4237,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128505057</v>
+        <v>128504656</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758900</v>
+        <v>758756</v>
       </c>
       <c r="R37" t="n">
-        <v>7202049</v>
+        <v>7201855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4312,7 +4320,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bild 3</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4339,10 +4347,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505058</v>
+        <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4374,10 +4382,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758801</v>
+        <v>758900</v>
       </c>
       <c r="R38" t="n">
-        <v>7201796</v>
+        <v>7202049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4410,6 +4418,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4436,53 +4449,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128504656</v>
+        <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758756</v>
+        <v>758801</v>
       </c>
       <c r="R39" t="n">
-        <v>7201855</v>
+        <v>7201796</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,11 +4520,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,7 +4549,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4643,10 +4643,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128504681</v>
+        <v>128504674</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758862</v>
+        <v>758861</v>
       </c>
       <c r="R41" t="n">
-        <v>7202121</v>
+        <v>7202117</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128504674</v>
+        <v>128504681</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>758861</v>
+        <v>758862</v>
       </c>
       <c r="R42" t="n">
-        <v>7202117</v>
+        <v>7202121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4643,7 +4643,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128504674</v>
+        <v>128504681</v>
       </c>
       <c r="B41" t="n">
         <v>98591</v>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758861</v>
+        <v>758862</v>
       </c>
       <c r="R41" t="n">
-        <v>7202117</v>
+        <v>7202121</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4740,7 +4740,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128504681</v>
+        <v>128504674</v>
       </c>
       <c r="B42" t="n">
         <v>98591</v>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>758862</v>
+        <v>758861</v>
       </c>
       <c r="R42" t="n">
-        <v>7202121</v>
+        <v>7202117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B35" t="n">
-        <v>80194</v>
+        <v>104060</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R35" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,11 +4109,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,32 +4135,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B36" t="n">
-        <v>104057</v>
+        <v>80194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4175,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R36" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,6 +4206,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,7 +4350,7 @@
         <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>104060</v>
+        <v>80221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R35" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,6 +4109,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4135,32 +4140,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>80194</v>
+        <v>104087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4175,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R36" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,11 +4211,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4237,53 +4237,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128504656</v>
+        <v>128505052</v>
       </c>
       <c r="B37" t="n">
-        <v>57689</v>
+        <v>104087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758756</v>
+        <v>758800</v>
       </c>
       <c r="R37" t="n">
-        <v>7201855</v>
+        <v>7201804</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4316,11 +4308,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4347,45 +4334,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505057</v>
+        <v>128504656</v>
       </c>
       <c r="B38" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758900</v>
+        <v>758756</v>
       </c>
       <c r="R38" t="n">
-        <v>7202049</v>
+        <v>7201855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4422,7 +4417,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Bild 3</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4449,10 +4444,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505058</v>
+        <v>128505057</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4484,10 +4479,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758801</v>
+        <v>758900</v>
       </c>
       <c r="R39" t="n">
-        <v>7201796</v>
+        <v>7202049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4520,6 +4515,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505052</v>
+        <v>128505058</v>
       </c>
       <c r="B40" t="n">
-        <v>104060</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758800</v>
+        <v>758801</v>
       </c>
       <c r="R40" t="n">
-        <v>7201804</v>
+        <v>7201796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4237,45 +4237,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128505052</v>
+        <v>128504656</v>
       </c>
       <c r="B37" t="n">
-        <v>104087</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758800</v>
+        <v>758756</v>
       </c>
       <c r="R37" t="n">
-        <v>7201804</v>
+        <v>7201855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4308,6 +4316,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4334,53 +4347,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R38" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4417,7 +4422,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4444,7 +4449,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505057</v>
+        <v>128505058</v>
       </c>
       <c r="B39" t="n">
         <v>98619</v>
@@ -4479,10 +4484,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758900</v>
+        <v>758801</v>
       </c>
       <c r="R39" t="n">
-        <v>7202049</v>
+        <v>7201796</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,11 +4520,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,32 +4546,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505058</v>
+        <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>104087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758801</v>
+        <v>758800</v>
       </c>
       <c r="R40" t="n">
-        <v>7201796</v>
+        <v>7201804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>104093</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R35" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,11 +4109,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,32 +4135,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B36" t="n">
-        <v>104087</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4175,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R36" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,6 +4206,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,7 +4350,7 @@
         <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -3944,7 +3944,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4038,32 +4038,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>104093</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R35" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,6 +4109,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4135,32 +4140,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>80225</v>
+        <v>104100</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4175,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R36" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4206,11 +4211,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4350,7 +4350,7 @@
         <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105456</v>
+        <v>105680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,14 +1389,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,14 +1490,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,14 +1591,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98457</v>
+        <v>98653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,14 +1692,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98457</v>
+        <v>98653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,14 +1793,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105471</v>
+        <v>105695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,14 +1894,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,14 +1995,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,14 +2096,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91677</v>
+        <v>91862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,14 +2197,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98457</v>
+        <v>98653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,14 +2298,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126531534</v>
       </c>
       <c r="B17" t="n">
-        <v>56849</v>
+        <v>56907</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,14 +2404,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80142</v>
+        <v>80253</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2461,14 +2505,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>103878</v>
+        <v>104100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2558,14 +2606,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>126531529</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,14 +2720,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80114</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,14 +2821,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91319</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,14 +2922,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80114</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,14 +3023,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98457</v>
+        <v>98653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,14 +3124,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,14 +3225,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105471</v>
+        <v>105695</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,14 +3326,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>126531532</v>
       </c>
       <c r="B27" t="n">
-        <v>57479</v>
+        <v>57537</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3355,14 +3435,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,14 +3536,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98457</v>
+        <v>98653</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3549,14 +3637,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3646,14 +3738,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98436</v>
+        <v>98632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3743,14 +3839,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80114</v>
+        <v>80225</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,14 +3940,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80114</v>
+        <v>80225</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3937,7 +4041,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,32 +4146,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B35" t="n">
-        <v>80225</v>
+        <v>104100</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4073,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R35" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,11 +4217,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4140,32 +4243,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B36" t="n">
-        <v>104100</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4175,10 +4278,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R36" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4211,6 +4314,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4237,53 +4345,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R37" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4320,7 +4420,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4347,7 +4447,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505057</v>
+        <v>128505058</v>
       </c>
       <c r="B38" t="n">
         <v>98632</v>
@@ -4382,10 +4482,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758900</v>
+        <v>758801</v>
       </c>
       <c r="R38" t="n">
-        <v>7202049</v>
+        <v>7201796</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4418,11 +4518,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4449,45 +4544,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505058</v>
+        <v>128504656</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758801</v>
+        <v>758756</v>
       </c>
       <c r="R39" t="n">
-        <v>7201796</v>
+        <v>7201855</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4520,6 +4623,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>126531534</v>
       </c>
       <c r="B17" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>126531529</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>126531532</v>
       </c>
       <c r="B27" t="n">
-        <v>57537</v>
+        <v>57541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4146,32 +4146,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128505054</v>
+        <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>104100</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758796</v>
+        <v>758866</v>
       </c>
       <c r="R35" t="n">
-        <v>7201797</v>
+        <v>7202091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4217,6 +4217,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4243,32 +4248,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128504665</v>
+        <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>80225</v>
+        <v>104104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4278,10 +4283,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758866</v>
+        <v>758796</v>
       </c>
       <c r="R36" t="n">
-        <v>7202091</v>
+        <v>7201797</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4314,11 +4319,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4345,45 +4345,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128505057</v>
+        <v>128504656</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758900</v>
+        <v>758756</v>
       </c>
       <c r="R37" t="n">
-        <v>7202049</v>
+        <v>7201855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4420,7 +4428,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bild 3</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4450,7 +4458,7 @@
         <v>128505058</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4544,53 +4552,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R39" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4657,7 +4657,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4751,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128504681</v>
+        <v>128504674</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758862</v>
+        <v>758861</v>
       </c>
       <c r="R41" t="n">
-        <v>7202121</v>
+        <v>7202117</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128504674</v>
+        <v>128504681</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>758861</v>
+        <v>758862</v>
       </c>
       <c r="R42" t="n">
-        <v>7202117</v>
+        <v>7202121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4948,7 +4948,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4552,32 +4552,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505057</v>
+        <v>128505052</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>104104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758900</v>
+        <v>758800</v>
       </c>
       <c r="R39" t="n">
-        <v>7202049</v>
+        <v>7201804</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,11 +4623,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4654,32 +4649,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505052</v>
+        <v>128505057</v>
       </c>
       <c r="B40" t="n">
-        <v>104104</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4684,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758800</v>
+        <v>758900</v>
       </c>
       <c r="R40" t="n">
-        <v>7201804</v>
+        <v>7202049</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4725,6 +4720,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4345,53 +4345,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128504656</v>
+        <v>128505052</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>104104</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758756</v>
+        <v>758800</v>
       </c>
       <c r="R37" t="n">
-        <v>7201855</v>
+        <v>7201804</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4424,11 +4416,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4455,45 +4442,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505058</v>
+        <v>128504656</v>
       </c>
       <c r="B38" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758801</v>
+        <v>758756</v>
       </c>
       <c r="R38" t="n">
-        <v>7201796</v>
+        <v>7201855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4526,6 +4521,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505052</v>
+        <v>128505057</v>
       </c>
       <c r="B39" t="n">
-        <v>104104</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758800</v>
+        <v>758900</v>
       </c>
       <c r="R39" t="n">
-        <v>7201804</v>
+        <v>7202049</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,6 +4623,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4649,7 +4654,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505057</v>
+        <v>128505058</v>
       </c>
       <c r="B40" t="n">
         <v>98636</v>
@@ -4684,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758900</v>
+        <v>758801</v>
       </c>
       <c r="R40" t="n">
-        <v>7202049</v>
+        <v>7201796</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4720,11 +4725,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4751,7 +4751,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128504674</v>
+        <v>128504681</v>
       </c>
       <c r="B41" t="n">
         <v>98636</v>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758861</v>
+        <v>758862</v>
       </c>
       <c r="R41" t="n">
-        <v>7202117</v>
+        <v>7202121</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128504681</v>
+        <v>128504674</v>
       </c>
       <c r="B42" t="n">
         <v>98636</v>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>758862</v>
+        <v>758861</v>
       </c>
       <c r="R42" t="n">
-        <v>7202121</v>
+        <v>7202117</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>126531534</v>
       </c>
       <c r="B17" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>126531529</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>126531532</v>
       </c>
       <c r="B27" t="n">
-        <v>57541</v>
+        <v>57544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4345,45 +4345,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128505052</v>
+        <v>128504656</v>
       </c>
       <c r="B37" t="n">
-        <v>104104</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758800</v>
+        <v>758756</v>
       </c>
       <c r="R37" t="n">
-        <v>7201804</v>
+        <v>7201855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4416,6 +4424,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,53 +4455,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R38" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4525,7 +4530,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4552,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505057</v>
+        <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758900</v>
+        <v>758801</v>
       </c>
       <c r="R39" t="n">
-        <v>7202049</v>
+        <v>7201796</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4623,11 +4628,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4654,32 +4654,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505058</v>
+        <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>104111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758801</v>
+        <v>758800</v>
       </c>
       <c r="R40" t="n">
-        <v>7201796</v>
+        <v>7201804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -4052,7 +4052,7 @@
         <v>128504673</v>
       </c>
       <c r="B34" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>128504665</v>
       </c>
       <c r="B35" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>128505054</v>
       </c>
       <c r="B36" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128505057</v>
       </c>
       <c r="B38" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>128505058</v>
       </c>
       <c r="B39" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>128505052</v>
       </c>
       <c r="B40" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>128504681</v>
       </c>
       <c r="B41" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>128504674</v>
       </c>
       <c r="B42" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>128504683</v>
       </c>
       <c r="B43" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97523</v>
+        <v>97528</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>128504664</v>
       </c>
       <c r="B45" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>128505060</v>
       </c>
       <c r="B46" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105699</v>
+        <v>105704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104119</v>
+        <v>104124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98685</v>
+        <v>98690</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105704</v>
+        <v>105707</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104124</v>
+        <v>104127</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98690</v>
+        <v>98693</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105707</v>
+        <v>105717</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>126531534</v>
       </c>
       <c r="B17" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>126531529</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>126531532</v>
       </c>
       <c r="B27" t="n">
-        <v>57544</v>
+        <v>57546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105717</v>
+        <v>105724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104137</v>
+        <v>104144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98703</v>
+        <v>98710</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105724</v>
+        <v>105726</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>126531534</v>
       </c>
       <c r="B17" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104144</v>
+        <v>104146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>126531529</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>126531532</v>
       </c>
       <c r="B27" t="n">
-        <v>57546</v>
+        <v>57548</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105726</v>
+        <v>105752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104146</v>
+        <v>104172</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105752</v>
+        <v>105754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104172</v>
+        <v>104174</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98738</v>
+        <v>98739</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105754</v>
+        <v>105755</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104174</v>
+        <v>104175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98739</v>
+        <v>98740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105755</v>
+        <v>105759</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104175</v>
+        <v>104179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98740</v>
+        <v>98744</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105759</v>
+        <v>105761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>126531566</v>
       </c>
       <c r="B18" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104179</v>
+        <v>104181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>126531575</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>126531580</v>
       </c>
       <c r="B23" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>126531618</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98744</v>
+        <v>98746</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>126531577</v>
       </c>
       <c r="B32" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>126531579</v>
       </c>
       <c r="B33" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
         <v>126531500</v>
       </c>
       <c r="B7" t="n">
-        <v>105761</v>
+        <v>105765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126531508</v>
       </c>
       <c r="B8" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126531505</v>
       </c>
       <c r="B9" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126531544</v>
       </c>
       <c r="B10" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>126531548</v>
       </c>
       <c r="B11" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>126531608</v>
       </c>
       <c r="B12" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>126531503</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126531509</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126531502</v>
       </c>
       <c r="B15" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>126531552</v>
       </c>
       <c r="B16" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>126531536</v>
       </c>
       <c r="B19" t="n">
-        <v>104181</v>
+        <v>104185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>126531510</v>
       </c>
       <c r="B22" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>126531546</v>
       </c>
       <c r="B24" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>126531610</v>
       </c>
       <c r="B26" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126531595</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126531551</v>
       </c>
       <c r="B29" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>126531569</v>
       </c>
       <c r="B30" t="n">
-        <v>98746</v>
+        <v>98750</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63606109</v>
+        <v>126531503</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalliden 4, Vb</t>
+          <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758781.6792293069</v>
+        <v>758834</v>
       </c>
       <c r="R2" t="n">
-        <v>7201955.551788761</v>
+        <v>7201929</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,34 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63606102</v>
+        <v>126531505</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,43 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalliden 4, Vb</t>
+          <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758730.2884000308</v>
+        <v>758910</v>
       </c>
       <c r="R3" t="n">
-        <v>7201921.17709689</v>
+        <v>7202078</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,61 +857,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammelskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>urgammal sälg</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea # urgammal sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63606115</v>
+        <v>126531508</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,43 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalliden 4, Vb</t>
+          <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758801.7590823962</v>
+        <v>758774</v>
       </c>
       <c r="R4" t="n">
-        <v>7201956.006675626</v>
+        <v>7202026</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,27 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63606096</v>
+        <v>126531509</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,43 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalliden 4, Vb</t>
+          <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758732.6379990412</v>
+        <v>758758</v>
       </c>
       <c r="R5" t="n">
-        <v>7201894.016983169</v>
+        <v>7201973</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,27 +1063,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63606123</v>
+        <v>126531510</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,43 +1090,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalliden 4, Vb</t>
+          <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758847.8780855908</v>
+        <v>758881</v>
       </c>
       <c r="R6" t="n">
-        <v>7201942.468370835</v>
+        <v>7201998</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,22 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-08-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,60 +1164,70 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126531500</v>
+        <v>63606109</v>
       </c>
       <c r="B7" t="n">
-        <v>105765</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röjmyrberget, Vb</t>
+          <t>Dalliden 4, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758915</v>
+        <v>758782</v>
       </c>
       <c r="R7" t="n">
-        <v>7202118</v>
+        <v>7201956</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,12 +1251,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,54 +1265,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126531508</v>
+        <v>126531502</v>
       </c>
       <c r="B8" t="n">
-        <v>91549</v>
+        <v>92281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758774</v>
+        <v>758757</v>
       </c>
       <c r="R8" t="n">
-        <v>7202026</v>
+        <v>7201974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,32 +1385,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126531505</v>
+        <v>126531618</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758910</v>
+        <v>758798</v>
       </c>
       <c r="R9" t="n">
-        <v>7202078</v>
+        <v>7201791</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,32 +1486,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126531544</v>
+        <v>126531619</v>
       </c>
       <c r="B10" t="n">
-        <v>98737</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758912</v>
+        <v>758947</v>
       </c>
       <c r="R10" t="n">
-        <v>7202106</v>
+        <v>7202120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,48 +1587,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126531548</v>
+        <v>63606096</v>
       </c>
       <c r="B11" t="n">
-        <v>98737</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röjmyrberget, Vb</t>
+          <t>Dalliden 4, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758798</v>
+        <v>758733</v>
       </c>
       <c r="R11" t="n">
-        <v>7201814</v>
+        <v>7201894</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1765,12 +1658,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,64 +1678,66 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126531608</v>
+        <v>63606102</v>
       </c>
       <c r="B12" t="n">
-        <v>105780</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Röjmyrberget, Vb</t>
+          <t>Dalliden 4, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758776</v>
+        <v>758730</v>
       </c>
       <c r="R12" t="n">
-        <v>7201970</v>
+        <v>7201921</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,12 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,30 +1777,56 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>gammelskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>urgammal sälg</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea # urgammal sälg</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126531503</v>
+        <v>63606115</v>
       </c>
       <c r="B13" t="n">
-        <v>91549</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1834,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Röjmyrberget, Vb</t>
+          <t>Dalliden 4, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758834</v>
+        <v>758802</v>
       </c>
       <c r="R13" t="n">
-        <v>7201929</v>
+        <v>7201956</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,12 +1894,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,26 +1914,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126531509</v>
+        <v>63606123</v>
       </c>
       <c r="B14" t="n">
-        <v>91549</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,37 +1937,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Röjmyrberget, Vb</t>
+          <t>Dalliden 4, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758758</v>
+        <v>758848</v>
       </c>
       <c r="R14" t="n">
-        <v>7201973</v>
+        <v>7201942</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,12 +1997,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2010-08-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,48 +2017,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126531502</v>
+        <v>126531575</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2139,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758757</v>
+        <v>758883</v>
       </c>
       <c r="R15" t="n">
-        <v>7201974</v>
+        <v>7202117</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,32 +2130,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126531552</v>
+        <v>126531577</v>
       </c>
       <c r="B16" t="n">
-        <v>98737</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758900</v>
+        <v>758824</v>
       </c>
       <c r="R16" t="n">
-        <v>7202051</v>
+        <v>7202146</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,32 +2231,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126531534</v>
+        <v>126531579</v>
       </c>
       <c r="B17" t="n">
-        <v>56917</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2341,10 +2266,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758902</v>
+        <v>758737</v>
       </c>
       <c r="R17" t="n">
-        <v>7202060</v>
+        <v>7201862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,11 +2302,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Tupp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2412,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126531566</v>
+        <v>126531580</v>
       </c>
       <c r="B18" t="n">
-        <v>80177</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758822</v>
+        <v>758845</v>
       </c>
       <c r="R18" t="n">
-        <v>7202153</v>
+        <v>7201911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126531536</v>
+        <v>128504664</v>
       </c>
       <c r="B19" t="n">
-        <v>104185</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2548,10 +2468,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>758765</v>
+        <v>758894</v>
       </c>
       <c r="R19" t="n">
-        <v>7201809</v>
+        <v>7202071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,12 +2498,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,18 +2526,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126531529</v>
+        <v>128504665</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,42 +2541,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>758759</v>
+        <v>758866</v>
       </c>
       <c r="R20" t="n">
-        <v>7201850</v>
+        <v>7202091</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,17 +2595,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,40 +2628,36 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126531575</v>
+        <v>126531566</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>80460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>758883</v>
+        <v>758822</v>
       </c>
       <c r="R21" t="n">
-        <v>7202117</v>
+        <v>7202153</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2829,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126531510</v>
+        <v>126531529</v>
       </c>
       <c r="B22" t="n">
-        <v>91549</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,34 +2744,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>758881</v>
+        <v>758759</v>
       </c>
       <c r="R22" t="n">
-        <v>7201998</v>
+        <v>7201850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,6 +2812,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126531580</v>
+        <v>128504654</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,34 +2858,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>758845</v>
+        <v>758754</v>
       </c>
       <c r="R23" t="n">
-        <v>7201911</v>
+        <v>7202005</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,12 +2920,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild 2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,53 +2953,57 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126531546</v>
+        <v>128504655</v>
       </c>
       <c r="B24" t="n">
-        <v>98737</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>758837</v>
+        <v>758742</v>
       </c>
       <c r="R24" t="n">
-        <v>7201925</v>
+        <v>7201971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,12 +3030,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,18 +3063,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126531618</v>
+        <v>128504656</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3143,34 +3078,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>758798</v>
+        <v>758756</v>
       </c>
       <c r="R25" t="n">
-        <v>7201791</v>
+        <v>7201855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,12 +3140,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,18 +3173,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126531610</v>
+        <v>126531534</v>
       </c>
       <c r="B26" t="n">
-        <v>105780</v>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,21 +3188,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3212,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>758880</v>
+        <v>758902</v>
       </c>
       <c r="R26" t="n">
-        <v>7201997</v>
+        <v>7202060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,6 +3248,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tupp</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,11 +3286,11 @@
         <v>126531532</v>
       </c>
       <c r="B27" t="n">
-        <v>57548</v>
+        <v>57774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3443,32 +3392,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126531595</v>
+        <v>126531569</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>99153</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3478,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>758795</v>
+        <v>758904</v>
       </c>
       <c r="R28" t="n">
-        <v>7201807</v>
+        <v>7202090</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,32 +3493,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126531551</v>
+        <v>126531595</v>
       </c>
       <c r="B29" t="n">
-        <v>98737</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3579,10 +3528,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758870</v>
+        <v>758795</v>
       </c>
       <c r="R29" t="n">
-        <v>7201971</v>
+        <v>7201807</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3645,32 +3594,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126531569</v>
+        <v>126531598</v>
       </c>
       <c r="B30" t="n">
-        <v>98750</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3680,10 +3629,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758904</v>
+        <v>758838</v>
       </c>
       <c r="R30" t="n">
-        <v>7202090</v>
+        <v>7201816</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3749,7 +3698,7 @@
         <v>126531600</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3847,32 +3796,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126531577</v>
+        <v>128504673</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3882,10 +3831,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>758824</v>
+        <v>758853</v>
       </c>
       <c r="R32" t="n">
-        <v>7202146</v>
+        <v>7202114</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3912,12 +3861,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3940,40 +3889,36 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126531579</v>
+        <v>128504674</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3983,10 +3928,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>758737</v>
+        <v>758861</v>
       </c>
       <c r="R33" t="n">
-        <v>7201862</v>
+        <v>7202117</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,12 +3958,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4041,18 +3986,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128504673</v>
+        <v>128504681</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,10 +4025,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>758853</v>
+        <v>758862</v>
       </c>
       <c r="R34" t="n">
-        <v>7202114</v>
+        <v>7202121</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,32 +4087,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128504665</v>
+        <v>128504683</v>
       </c>
       <c r="B35" t="n">
-        <v>80139</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +4122,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>758866</v>
+        <v>758882</v>
       </c>
       <c r="R35" t="n">
-        <v>7202091</v>
+        <v>7202131</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4221,7 +4162,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bild 6</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4248,32 +4189,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128505054</v>
+        <v>128505056</v>
       </c>
       <c r="B36" t="n">
-        <v>104119</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4283,10 +4224,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>758796</v>
+        <v>758882</v>
       </c>
       <c r="R36" t="n">
-        <v>7201797</v>
+        <v>7201992</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4345,53 +4286,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128504656</v>
+        <v>128505057</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>758756</v>
+        <v>758900</v>
       </c>
       <c r="R37" t="n">
-        <v>7201855</v>
+        <v>7202049</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4428,7 +4361,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4455,10 +4388,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128505057</v>
+        <v>128505058</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4490,10 +4423,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>758900</v>
+        <v>758801</v>
       </c>
       <c r="R38" t="n">
-        <v>7202049</v>
+        <v>7201796</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4526,11 +4459,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bild 3</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4557,10 +4485,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128505058</v>
+        <v>128505059</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4592,10 +4520,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>758801</v>
+        <v>758884</v>
       </c>
       <c r="R39" t="n">
-        <v>7201796</v>
+        <v>7202001</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,32 +4582,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128505052</v>
+        <v>128505060</v>
       </c>
       <c r="B40" t="n">
-        <v>104119</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4689,10 +4617,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>758800</v>
+        <v>758897</v>
       </c>
       <c r="R40" t="n">
-        <v>7201804</v>
+        <v>7202042</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4725,6 +4653,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bild 4</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4751,32 +4684,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128504681</v>
+        <v>126531608</v>
       </c>
       <c r="B41" t="n">
-        <v>98651</v>
+        <v>106243</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4786,10 +4719,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>758862</v>
+        <v>758776</v>
       </c>
       <c r="R41" t="n">
-        <v>7202121</v>
+        <v>7201970</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4816,12 +4749,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4844,36 +4777,40 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128504674</v>
+        <v>126531610</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>106243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4883,10 +4820,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>758861</v>
+        <v>758880</v>
       </c>
       <c r="R42" t="n">
-        <v>7202117</v>
+        <v>7201997</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4913,12 +4850,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4941,36 +4878,40 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128504683</v>
+        <v>126531500</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>106228</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4980,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>758882</v>
+        <v>758915</v>
       </c>
       <c r="R43" t="n">
-        <v>7202131</v>
+        <v>7202118</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5010,17 +4951,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Bild 6</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5043,14 +4979,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>128504658</v>
       </c>
       <c r="B44" t="n">
-        <v>97528</v>
+        <v>97989</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5144,32 +5084,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128504664</v>
+        <v>126531544</v>
       </c>
       <c r="B45" t="n">
-        <v>80139</v>
+        <v>99140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5179,10 +5119,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>758894</v>
+        <v>758912</v>
       </c>
       <c r="R45" t="n">
-        <v>7202071</v>
+        <v>7202106</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5209,12 +5149,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5237,36 +5177,40 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128505060</v>
+        <v>126531546</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>99140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5276,10 +5220,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>758897</v>
+        <v>758837</v>
       </c>
       <c r="R46" t="n">
-        <v>7202042</v>
+        <v>7201925</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,17 +5250,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bild 4</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5339,7 +5278,815 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126531548</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>758798</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7201814</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126531551</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>758870</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7201971</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126531552</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>758900</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7202051</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126531555</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>758916</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7202084</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126531536</v>
+      </c>
+      <c r="B51" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>758765</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7201809</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128505052</v>
+      </c>
+      <c r="B52" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>758800</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7201804</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128505054</v>
+      </c>
+      <c r="B53" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>758796</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7201797</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126531628</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92285</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6331024</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Skeletocutis delicata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Röjmyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>758910</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7202074</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På död ullticka. Skulle väl kunna vara S.exilis också, men den växer vad jag förstår inte särskilt ofta på ullticka. Hade inte skadat att mikra, tog kollekt.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31718-2025 artfynd.xlsx
+++ b/artfynd/A 31718-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531509</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531510</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531618</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1584,6 +1629,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531619</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606096</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606102</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1923,6 +1983,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606115</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63606123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531575</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531577</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531579</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531580</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504664</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504665</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531566</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531529</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2954,6 +3064,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504654</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3064,6 +3179,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504655</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3174,6 +3294,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504656</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3280,6 +3405,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531534</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3389,6 +3519,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531532</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3490,6 +3625,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531569</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3591,6 +3731,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531595</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3692,6 +3837,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531598</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3793,6 +3943,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531600</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3890,6 +4045,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504673</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3987,6 +4147,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504674</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4084,6 +4249,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504681</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4186,6 +4356,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504683</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4283,6 +4458,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505056</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4385,6 +4565,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505057</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4482,6 +4667,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505058</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4579,6 +4769,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505059</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4681,6 +4876,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505060</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4782,6 +4982,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531608</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4883,6 +5088,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531610</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4984,6 +5194,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531500</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5081,6 +5296,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128504658</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5182,6 +5402,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531544</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5283,6 +5508,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531546</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5384,6 +5614,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531548</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5485,6 +5720,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531551</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5586,6 +5826,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531552</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5687,6 +5932,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531555</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5788,6 +6038,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531536</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5885,6 +6140,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5982,6 +6242,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128505054</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6087,8 +6352,68 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126531628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>